--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 лгрсч пок зпф (нет).xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/10,09,26 ПОКОМ ЗПФ/дв 10,09,26 лгрсч пок зпф (нет).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\10,09,26 ПОКОМ ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02E4CC5-8C4E-4AB9-B7E8-EE5AD9E8775C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F104DF3-4B62-4E9B-A86D-22217134AE0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AM$71</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029" refMode="R1C1"/>
 </workbook>
 </file>
 
@@ -1050,7 +1042,8 @@
     <col min="36" max="36" width="6" customWidth="1"/>
     <col min="37" max="38" width="5" customWidth="1"/>
     <col min="39" max="39" width="6" style="11" customWidth="1"/>
-    <col min="40" max="49" width="3" customWidth="1"/>
+    <col min="40" max="40" width="6.5703125" customWidth="1"/>
+    <col min="41" max="49" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:49" x14ac:dyDescent="0.25">
@@ -1478,7 +1471,10 @@
         <f>SUM(AM6:AM499)</f>
         <v>8.954761904761904</v>
       </c>
-      <c r="AN5" s="16"/>
+      <c r="AN5" s="3">
+        <f>SUM(AN6:AN499)</f>
+        <v>2127.6840000000007</v>
+      </c>
       <c r="AO5" s="16"/>
       <c r="AP5" s="16"/>
       <c r="AQ5" s="16"/>
@@ -1581,7 +1577,10 @@
       <c r="AK6" s="12"/>
       <c r="AL6" s="12"/>
       <c r="AM6" s="15"/>
-      <c r="AN6" s="16"/>
+      <c r="AN6" s="16">
+        <f>Q6*G6</f>
+        <v>0</v>
+      </c>
       <c r="AO6" s="16"/>
       <c r="AP6" s="16"/>
       <c r="AQ6" s="16"/>
@@ -1684,7 +1683,10 @@
       <c r="AK7" s="12"/>
       <c r="AL7" s="12"/>
       <c r="AM7" s="15"/>
-      <c r="AN7" s="16"/>
+      <c r="AN7" s="16">
+        <f t="shared" ref="AN7:AN70" si="6">Q7*G7</f>
+        <v>0</v>
+      </c>
       <c r="AO7" s="16"/>
       <c r="AP7" s="16"/>
       <c r="AQ7" s="16"/>
@@ -1812,7 +1814,10 @@
         <f>AI8/AL8</f>
         <v>0</v>
       </c>
-      <c r="AN8" s="16"/>
+      <c r="AN8" s="16">
+        <f t="shared" si="6"/>
+        <v>2.6839999999999997</v>
+      </c>
       <c r="AO8" s="16"/>
       <c r="AP8" s="16"/>
       <c r="AQ8" s="16"/>
@@ -1940,7 +1945,10 @@
         <f>AI9/AL9</f>
         <v>0</v>
       </c>
-      <c r="AN9" s="16"/>
+      <c r="AN9" s="16">
+        <f t="shared" si="6"/>
+        <v>5.34</v>
+      </c>
       <c r="AO9" s="16"/>
       <c r="AP9" s="16"/>
       <c r="AQ9" s="16"/>
@@ -2041,7 +2049,10 @@
       <c r="AK10" s="12"/>
       <c r="AL10" s="12"/>
       <c r="AM10" s="15"/>
-      <c r="AN10" s="16"/>
+      <c r="AN10" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO10" s="16"/>
       <c r="AP10" s="16"/>
       <c r="AQ10" s="16"/>
@@ -2169,7 +2180,10 @@
         <f>AI11/AL11</f>
         <v>0</v>
       </c>
-      <c r="AN11" s="16"/>
+      <c r="AN11" s="16">
+        <f t="shared" si="6"/>
+        <v>29.344000000000001</v>
+      </c>
       <c r="AO11" s="16"/>
       <c r="AP11" s="16"/>
       <c r="AQ11" s="16"/>
@@ -2297,7 +2311,10 @@
         <f>AI12/AL12</f>
         <v>0</v>
       </c>
-      <c r="AN12" s="16"/>
+      <c r="AN12" s="16">
+        <f t="shared" si="6"/>
+        <v>20.303999999999998</v>
+      </c>
       <c r="AO12" s="16"/>
       <c r="AP12" s="16"/>
       <c r="AQ12" s="16"/>
@@ -2398,7 +2415,10 @@
       <c r="AK13" s="12"/>
       <c r="AL13" s="12"/>
       <c r="AM13" s="15"/>
-      <c r="AN13" s="16"/>
+      <c r="AN13" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO13" s="16"/>
       <c r="AP13" s="16"/>
       <c r="AQ13" s="16"/>
@@ -2528,7 +2548,10 @@
         <f>AI14/AL14</f>
         <v>0</v>
       </c>
-      <c r="AN14" s="16"/>
+      <c r="AN14" s="16">
+        <f t="shared" si="6"/>
+        <v>41.28</v>
+      </c>
       <c r="AO14" s="16"/>
       <c r="AP14" s="16"/>
       <c r="AQ14" s="16"/>
@@ -2588,7 +2611,7 @@
         <v>113</v>
       </c>
       <c r="R15" s="4">
-        <f t="shared" ref="R15" si="6">14*Q15-P15-O15-F15</f>
+        <f t="shared" ref="R15" si="7">14*Q15-P15-O15-F15</f>
         <v>88</v>
       </c>
       <c r="S15" s="4">
@@ -2659,7 +2682,10 @@
         <f>AI15/AL15</f>
         <v>0.2</v>
       </c>
-      <c r="AN15" s="16"/>
+      <c r="AN15" s="16">
+        <f t="shared" si="6"/>
+        <v>27.119999999999997</v>
+      </c>
       <c r="AO15" s="16"/>
       <c r="AP15" s="16"/>
       <c r="AQ15" s="16"/>
@@ -2756,7 +2782,10 @@
       <c r="AK16" s="12"/>
       <c r="AL16" s="12"/>
       <c r="AM16" s="15"/>
-      <c r="AN16" s="16"/>
+      <c r="AN16" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO16" s="16"/>
       <c r="AP16" s="16"/>
       <c r="AQ16" s="16"/>
@@ -2853,7 +2882,10 @@
       <c r="AK17" s="12"/>
       <c r="AL17" s="12"/>
       <c r="AM17" s="15"/>
-      <c r="AN17" s="16"/>
+      <c r="AN17" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO17" s="16"/>
       <c r="AP17" s="16"/>
       <c r="AQ17" s="16"/>
@@ -2916,7 +2948,7 @@
       </c>
       <c r="R18" s="4"/>
       <c r="S18" s="4">
-        <f t="shared" ref="S18:S49" si="7">AH18*AI18</f>
+        <f t="shared" ref="S18:S49" si="8">AH18*AI18</f>
         <v>0</v>
       </c>
       <c r="T18" s="16">
@@ -2959,18 +2991,18 @@
       </c>
       <c r="AF18" s="16"/>
       <c r="AG18" s="16">
-        <f t="shared" ref="AG18:AG49" si="8">G18*R18</f>
+        <f t="shared" ref="AG18:AG49" si="9">G18*R18</f>
         <v>0</v>
       </c>
       <c r="AH18" s="6">
         <v>12</v>
       </c>
       <c r="AI18" s="8">
-        <f t="shared" ref="AI18:AI49" si="9">MROUND(R18, AH18*AK18)/AH18</f>
+        <f t="shared" ref="AI18:AI49" si="10">MROUND(R18, AH18*AK18)/AH18</f>
         <v>0</v>
       </c>
       <c r="AJ18" s="16">
-        <f t="shared" ref="AJ18:AJ49" si="10">AI18*AH18*G18</f>
+        <f t="shared" ref="AJ18:AJ49" si="11">AI18*AH18*G18</f>
         <v>0</v>
       </c>
       <c r="AK18" s="16">
@@ -2980,10 +3012,13 @@
         <v>70</v>
       </c>
       <c r="AM18" s="8">
-        <f t="shared" ref="AM18:AM49" si="11">AI18/AL18</f>
-        <v>0</v>
-      </c>
-      <c r="AN18" s="16"/>
+        <f t="shared" ref="AM18:AM49" si="12">AI18/AL18</f>
+        <v>0</v>
+      </c>
+      <c r="AN18" s="16">
+        <f t="shared" si="6"/>
+        <v>40.559999999999995</v>
+      </c>
       <c r="AO18" s="16"/>
       <c r="AP18" s="16"/>
       <c r="AQ18" s="16"/>
@@ -3048,7 +3083,7 @@
         <v>84</v>
       </c>
       <c r="S19" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>112</v>
       </c>
       <c r="T19" s="16">
@@ -3091,18 +3126,18 @@
       </c>
       <c r="AF19" s="16"/>
       <c r="AG19" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>40.32</v>
       </c>
       <c r="AH19" s="6">
         <v>8</v>
       </c>
       <c r="AI19" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AJ19" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>53.76</v>
       </c>
       <c r="AK19" s="16">
@@ -3112,10 +3147,13 @@
         <v>70</v>
       </c>
       <c r="AM19" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AN19" s="16"/>
+      <c r="AN19" s="16">
+        <f t="shared" si="6"/>
+        <v>15.552</v>
+      </c>
       <c r="AO19" s="16"/>
       <c r="AP19" s="16"/>
       <c r="AQ19" s="16"/>
@@ -3176,7 +3214,7 @@
       </c>
       <c r="R20" s="4"/>
       <c r="S20" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T20" s="16">
@@ -3219,18 +3257,18 @@
       </c>
       <c r="AF20" s="16"/>
       <c r="AG20" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH20" s="6">
         <v>24</v>
       </c>
       <c r="AI20" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ20" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK20" s="16">
@@ -3240,10 +3278,13 @@
         <v>126</v>
       </c>
       <c r="AM20" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN20" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN20" s="16">
+        <f t="shared" si="6"/>
+        <v>11.592000000000001</v>
+      </c>
       <c r="AO20" s="16"/>
       <c r="AP20" s="16"/>
       <c r="AQ20" s="16"/>
@@ -3304,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="S21" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T21" s="16">
@@ -3349,18 +3390,18 @@
         <v>73</v>
       </c>
       <c r="AG21" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH21" s="6">
         <v>10</v>
       </c>
       <c r="AI21" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ21" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK21" s="16">
@@ -3370,10 +3411,13 @@
         <v>70</v>
       </c>
       <c r="AM21" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN21" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN21" s="16">
+        <f t="shared" si="6"/>
+        <v>12.167999999999999</v>
+      </c>
       <c r="AO21" s="16"/>
       <c r="AP21" s="16"/>
       <c r="AQ21" s="16"/>
@@ -3433,11 +3477,11 @@
         <v>52.4</v>
       </c>
       <c r="R22" s="4">
-        <f t="shared" ref="R22:R71" si="12">14*Q22-P22-O22-F22</f>
+        <f t="shared" ref="R22:R71" si="13">14*Q22-P22-O22-F22</f>
         <v>234.60000000000002</v>
       </c>
       <c r="S22" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>168</v>
       </c>
       <c r="T22" s="16">
@@ -3480,18 +3524,18 @@
       </c>
       <c r="AF22" s="16"/>
       <c r="AG22" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>46.920000000000009</v>
       </c>
       <c r="AH22" s="6">
         <v>12</v>
       </c>
       <c r="AI22" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AJ22" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>33.6</v>
       </c>
       <c r="AK22" s="16">
@@ -3501,10 +3545,13 @@
         <v>70</v>
       </c>
       <c r="AM22" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AN22" s="16"/>
+      <c r="AN22" s="16">
+        <f t="shared" si="6"/>
+        <v>10.48</v>
+      </c>
       <c r="AO22" s="16"/>
       <c r="AP22" s="16"/>
       <c r="AQ22" s="16"/>
@@ -3565,7 +3612,7 @@
       </c>
       <c r="R23" s="4"/>
       <c r="S23" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T23" s="16">
@@ -3610,18 +3657,18 @@
         <v>96</v>
       </c>
       <c r="AG23" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH23" s="6">
         <v>12</v>
       </c>
       <c r="AI23" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ23" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK23" s="16">
@@ -3631,10 +3678,13 @@
         <v>70</v>
       </c>
       <c r="AM23" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN23" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN23" s="16">
+        <f t="shared" si="6"/>
+        <v>12.240000000000002</v>
+      </c>
       <c r="AO23" s="16"/>
       <c r="AP23" s="16"/>
       <c r="AQ23" s="16"/>
@@ -3694,11 +3744,11 @@
         <v>57.720000000000006</v>
       </c>
       <c r="R24" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>130.98000000000008</v>
       </c>
       <c r="S24" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>155.4</v>
       </c>
       <c r="T24" s="16">
@@ -3741,18 +3791,18 @@
       </c>
       <c r="AF24" s="16"/>
       <c r="AG24" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130.98000000000008</v>
       </c>
       <c r="AH24" s="6">
         <v>3.7</v>
       </c>
       <c r="AI24" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>42</v>
       </c>
       <c r="AJ24" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>155.4</v>
       </c>
       <c r="AK24" s="16">
@@ -3762,10 +3812,13 @@
         <v>126</v>
       </c>
       <c r="AM24" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AN24" s="16"/>
+      <c r="AN24" s="16">
+        <f t="shared" si="6"/>
+        <v>57.720000000000006</v>
+      </c>
       <c r="AO24" s="16"/>
       <c r="AP24" s="16"/>
       <c r="AQ24" s="16"/>
@@ -3826,7 +3879,7 @@
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T25" s="16">
@@ -3869,18 +3922,18 @@
       </c>
       <c r="AF25" s="16"/>
       <c r="AG25" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH25" s="6">
         <v>5.5</v>
       </c>
       <c r="AI25" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ25" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK25" s="16">
@@ -3890,10 +3943,13 @@
         <v>84</v>
       </c>
       <c r="AM25" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN25" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN25" s="16">
+        <f t="shared" si="6"/>
+        <v>19.5</v>
+      </c>
       <c r="AO25" s="16"/>
       <c r="AP25" s="16"/>
       <c r="AQ25" s="16"/>
@@ -3953,11 +4009,11 @@
         <v>56.7</v>
       </c>
       <c r="R26" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>96.300000000000068</v>
       </c>
       <c r="S26" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>84</v>
       </c>
       <c r="T26" s="16">
@@ -4000,18 +4056,18 @@
       </c>
       <c r="AF26" s="16"/>
       <c r="AG26" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>96.300000000000068</v>
       </c>
       <c r="AH26" s="6">
         <v>3</v>
       </c>
       <c r="AI26" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="AJ26" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AK26" s="16">
@@ -4021,10 +4077,13 @@
         <v>126</v>
       </c>
       <c r="AM26" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.22222222222222221</v>
       </c>
-      <c r="AN26" s="16"/>
+      <c r="AN26" s="16">
+        <f t="shared" si="6"/>
+        <v>56.7</v>
+      </c>
       <c r="AO26" s="16"/>
       <c r="AP26" s="16"/>
       <c r="AQ26" s="16"/>
@@ -4087,7 +4146,7 @@
       </c>
       <c r="R27" s="4"/>
       <c r="S27" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T27" s="16">
@@ -4130,18 +4189,18 @@
       </c>
       <c r="AF27" s="16"/>
       <c r="AG27" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH27" s="6">
         <v>6</v>
       </c>
       <c r="AI27" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ27" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK27" s="16">
@@ -4151,10 +4210,13 @@
         <v>140</v>
       </c>
       <c r="AM27" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN27" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN27" s="16">
+        <f t="shared" si="6"/>
+        <v>18.649999999999999</v>
+      </c>
       <c r="AO27" s="16"/>
       <c r="AP27" s="16"/>
       <c r="AQ27" s="16"/>
@@ -4215,7 +4277,7 @@
       </c>
       <c r="R28" s="4"/>
       <c r="S28" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T28" s="16">
@@ -4258,18 +4320,18 @@
       </c>
       <c r="AF28" s="16"/>
       <c r="AG28" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH28" s="6">
         <v>6</v>
       </c>
       <c r="AI28" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ28" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK28" s="16">
@@ -4279,10 +4341,13 @@
         <v>140</v>
       </c>
       <c r="AM28" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN28" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN28" s="16">
+        <f t="shared" si="6"/>
+        <v>9.85</v>
+      </c>
       <c r="AO28" s="16"/>
       <c r="AP28" s="16"/>
       <c r="AQ28" s="16"/>
@@ -4342,11 +4407,11 @@
         <v>181.4</v>
       </c>
       <c r="R29" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>960.59999999999991</v>
       </c>
       <c r="S29" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>936</v>
       </c>
       <c r="T29" s="16">
@@ -4389,18 +4454,18 @@
       </c>
       <c r="AF29" s="16"/>
       <c r="AG29" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>960.59999999999991</v>
       </c>
       <c r="AH29" s="6">
         <v>6</v>
       </c>
       <c r="AI29" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>156</v>
       </c>
       <c r="AJ29" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>936</v>
       </c>
       <c r="AK29" s="16">
@@ -4410,10 +4475,13 @@
         <v>84</v>
       </c>
       <c r="AM29" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>1.8571428571428572</v>
       </c>
-      <c r="AN29" s="16"/>
+      <c r="AN29" s="16">
+        <f t="shared" si="6"/>
+        <v>181.4</v>
+      </c>
       <c r="AO29" s="16"/>
       <c r="AP29" s="16"/>
       <c r="AQ29" s="16"/>
@@ -4473,11 +4541,11 @@
         <v>59</v>
       </c>
       <c r="R30" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>133</v>
       </c>
       <c r="S30" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>168</v>
       </c>
       <c r="T30" s="16">
@@ -4520,18 +4588,18 @@
       </c>
       <c r="AF30" s="16"/>
       <c r="AG30" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>30.59</v>
       </c>
       <c r="AH30" s="6">
         <v>12</v>
       </c>
       <c r="AI30" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>14</v>
       </c>
       <c r="AJ30" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>38.64</v>
       </c>
       <c r="AK30" s="16">
@@ -4541,10 +4609,13 @@
         <v>70</v>
       </c>
       <c r="AM30" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.2</v>
       </c>
-      <c r="AN30" s="16"/>
+      <c r="AN30" s="16">
+        <f t="shared" si="6"/>
+        <v>13.57</v>
+      </c>
       <c r="AO30" s="16"/>
       <c r="AP30" s="16"/>
       <c r="AQ30" s="16"/>
@@ -4605,7 +4676,7 @@
       </c>
       <c r="R31" s="4"/>
       <c r="S31" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T31" s="16">
@@ -4648,18 +4719,18 @@
       </c>
       <c r="AF31" s="16"/>
       <c r="AG31" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH31" s="6">
         <v>12</v>
       </c>
       <c r="AI31" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ31" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK31" s="16">
@@ -4669,10 +4740,13 @@
         <v>70</v>
       </c>
       <c r="AM31" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN31" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN31" s="16">
+        <f t="shared" si="6"/>
+        <v>23.2</v>
+      </c>
       <c r="AO31" s="16"/>
       <c r="AP31" s="16"/>
       <c r="AQ31" s="16"/>
@@ -4733,7 +4807,7 @@
       </c>
       <c r="R32" s="4"/>
       <c r="S32" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T32" s="16">
@@ -4776,18 +4850,18 @@
       </c>
       <c r="AF32" s="16"/>
       <c r="AG32" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH32" s="6">
         <v>12</v>
       </c>
       <c r="AI32" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ32" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK32" s="16">
@@ -4797,10 +4871,13 @@
         <v>70</v>
       </c>
       <c r="AM32" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN32" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN32" s="16">
+        <f t="shared" si="6"/>
+        <v>15.8</v>
+      </c>
       <c r="AO32" s="16"/>
       <c r="AP32" s="16"/>
       <c r="AQ32" s="16"/>
@@ -4860,11 +4937,11 @@
         <v>86.6</v>
       </c>
       <c r="R33" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>282.39999999999986</v>
       </c>
       <c r="S33" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>336</v>
       </c>
       <c r="T33" s="16">
@@ -4907,18 +4984,18 @@
       </c>
       <c r="AF33" s="16"/>
       <c r="AG33" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>70.599999999999966</v>
       </c>
       <c r="AH33" s="6">
         <v>12</v>
       </c>
       <c r="AI33" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="AJ33" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AK33" s="16">
@@ -4928,10 +5005,13 @@
         <v>70</v>
       </c>
       <c r="AM33" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.4</v>
       </c>
-      <c r="AN33" s="16"/>
+      <c r="AN33" s="16">
+        <f t="shared" si="6"/>
+        <v>21.65</v>
+      </c>
       <c r="AO33" s="16"/>
       <c r="AP33" s="16"/>
       <c r="AQ33" s="16"/>
@@ -4990,7 +5070,7 @@
       </c>
       <c r="R34" s="4"/>
       <c r="S34" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T34" s="16">
@@ -5033,18 +5113,18 @@
       </c>
       <c r="AF34" s="16"/>
       <c r="AG34" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH34" s="6">
         <v>12</v>
       </c>
       <c r="AI34" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ34" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK34" s="16">
@@ -5054,10 +5134,13 @@
         <v>70</v>
       </c>
       <c r="AM34" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN34" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN34" s="16">
+        <f t="shared" si="6"/>
+        <v>3.45</v>
+      </c>
       <c r="AO34" s="16"/>
       <c r="AP34" s="16"/>
       <c r="AQ34" s="16"/>
@@ -5118,7 +5201,7 @@
       </c>
       <c r="R35" s="4"/>
       <c r="S35" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T35" s="16">
@@ -5161,18 +5244,18 @@
       </c>
       <c r="AF35" s="16"/>
       <c r="AG35" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH35" s="6">
         <v>8</v>
       </c>
       <c r="AI35" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ35" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK35" s="16">
@@ -5182,10 +5265,13 @@
         <v>84</v>
       </c>
       <c r="AM35" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN35" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN35" s="16">
+        <f t="shared" si="6"/>
+        <v>19.179999999999996</v>
+      </c>
       <c r="AO35" s="16"/>
       <c r="AP35" s="16"/>
       <c r="AQ35" s="16"/>
@@ -5246,7 +5332,7 @@
       </c>
       <c r="R36" s="4"/>
       <c r="S36" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T36" s="16">
@@ -5289,18 +5375,18 @@
       </c>
       <c r="AF36" s="16"/>
       <c r="AG36" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH36" s="6">
         <v>8</v>
       </c>
       <c r="AI36" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ36" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK36" s="16">
@@ -5310,10 +5396,13 @@
         <v>84</v>
       </c>
       <c r="AM36" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN36" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN36" s="16">
+        <f t="shared" si="6"/>
+        <v>22.54</v>
+      </c>
       <c r="AO36" s="16"/>
       <c r="AP36" s="16"/>
       <c r="AQ36" s="16"/>
@@ -5372,7 +5461,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="21">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T37" s="16">
@@ -5417,18 +5506,18 @@
         <v>73</v>
       </c>
       <c r="AG37" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH37" s="6">
         <v>8</v>
       </c>
       <c r="AI37" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ37" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK37" s="16">
@@ -5438,10 +5527,13 @@
         <v>84</v>
       </c>
       <c r="AM37" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN37" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN37" s="16">
+        <f t="shared" si="6"/>
+        <v>0.27999999999999997</v>
+      </c>
       <c r="AO37" s="16"/>
       <c r="AP37" s="16"/>
       <c r="AQ37" s="16"/>
@@ -5485,7 +5577,7 @@
         <v>139</v>
       </c>
       <c r="L38" s="16">
-        <f t="shared" ref="L38:L69" si="13">E38-K38</f>
+        <f t="shared" ref="L38:L69" si="14">E38-K38</f>
         <v>-7</v>
       </c>
       <c r="M38" s="16"/>
@@ -5497,20 +5589,20 @@
         <v>120</v>
       </c>
       <c r="Q38" s="16">
-        <f t="shared" ref="Q38:Q71" si="14">E38/5</f>
+        <f t="shared" ref="Q38:Q71" si="15">E38/5</f>
         <v>26.4</v>
       </c>
       <c r="R38" s="4"/>
       <c r="S38" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T38" s="16">
-        <f t="shared" ref="T38:T69" si="15">(F38+O38+P38+S38)/Q38</f>
+        <f t="shared" ref="T38:T69" si="16">(F38+O38+P38+S38)/Q38</f>
         <v>15.568181818181818</v>
       </c>
       <c r="U38" s="16">
-        <f t="shared" ref="U38:U71" si="16">(F38+O38+P38)/Q38</f>
+        <f t="shared" ref="U38:U71" si="17">(F38+O38+P38)/Q38</f>
         <v>15.568181818181818</v>
       </c>
       <c r="V38" s="16">
@@ -5545,18 +5637,18 @@
       </c>
       <c r="AF38" s="16"/>
       <c r="AG38" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH38" s="6">
         <v>10</v>
       </c>
       <c r="AI38" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ38" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK38" s="16">
@@ -5566,10 +5658,13 @@
         <v>84</v>
       </c>
       <c r="AM38" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN38" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN38" s="16">
+        <f t="shared" si="6"/>
+        <v>18.479999999999997</v>
+      </c>
       <c r="AO38" s="16"/>
       <c r="AP38" s="16"/>
       <c r="AQ38" s="16"/>
@@ -5605,7 +5700,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-21</v>
       </c>
       <c r="M39" s="16"/>
@@ -5617,22 +5712,22 @@
         <v>240</v>
       </c>
       <c r="Q39" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R39" s="4"/>
       <c r="S39" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T39" s="16" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U39" s="16" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U39" s="16" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V39" s="16">
         <v>0</v>
       </c>
@@ -5667,18 +5762,18 @@
         <v>111</v>
       </c>
       <c r="AG39" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH39" s="6">
         <v>10</v>
       </c>
       <c r="AI39" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ39" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK39" s="16">
@@ -5688,10 +5783,13 @@
         <v>84</v>
       </c>
       <c r="AM39" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN39" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN39" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO39" s="16"/>
       <c r="AP39" s="16"/>
       <c r="AQ39" s="16"/>
@@ -5735,7 +5833,7 @@
         <v>212</v>
       </c>
       <c r="L40" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M40" s="16"/>
@@ -5747,23 +5845,23 @@
         <v>360</v>
       </c>
       <c r="Q40" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42.4</v>
       </c>
       <c r="R40" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>90.600000000000023</v>
       </c>
       <c r="S40" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="T40" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14.693396226415095</v>
       </c>
       <c r="U40" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.863207547169811</v>
       </c>
       <c r="V40" s="16">
@@ -5798,18 +5896,18 @@
       </c>
       <c r="AF40" s="16"/>
       <c r="AG40" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>63.420000000000009</v>
       </c>
       <c r="AH40" s="6">
         <v>10</v>
       </c>
       <c r="AI40" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="AJ40" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AK40" s="16">
@@ -5819,10 +5917,13 @@
         <v>84</v>
       </c>
       <c r="AM40" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN40" s="16"/>
+      <c r="AN40" s="16">
+        <f t="shared" si="6"/>
+        <v>29.679999999999996</v>
+      </c>
       <c r="AO40" s="16"/>
       <c r="AP40" s="16"/>
       <c r="AQ40" s="16"/>
@@ -5864,7 +5965,7 @@
         <v>126</v>
       </c>
       <c r="L41" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-10</v>
       </c>
       <c r="M41" s="16"/>
@@ -5876,23 +5977,23 @@
         <v>240</v>
       </c>
       <c r="Q41" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>23.2</v>
       </c>
       <c r="R41" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>86.800000000000011</v>
       </c>
       <c r="S41" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>120</v>
       </c>
       <c r="T41" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>15.431034482758621</v>
       </c>
       <c r="U41" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10.258620689655173</v>
       </c>
       <c r="V41" s="16">
@@ -5927,18 +6028,18 @@
       </c>
       <c r="AF41" s="16"/>
       <c r="AG41" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>60.760000000000005</v>
       </c>
       <c r="AH41" s="6">
         <v>10</v>
       </c>
       <c r="AI41" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>12</v>
       </c>
       <c r="AJ41" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>84</v>
       </c>
       <c r="AK41" s="16">
@@ -5948,10 +6049,13 @@
         <v>84</v>
       </c>
       <c r="AM41" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.14285714285714285</v>
       </c>
-      <c r="AN41" s="16"/>
+      <c r="AN41" s="16">
+        <f t="shared" si="6"/>
+        <v>16.239999999999998</v>
+      </c>
       <c r="AO41" s="16"/>
       <c r="AP41" s="16"/>
       <c r="AQ41" s="16"/>
@@ -5995,7 +6099,7 @@
         <v>925</v>
       </c>
       <c r="L42" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-20</v>
       </c>
       <c r="M42" s="16"/>
@@ -6007,23 +6111,23 @@
         <v>1560</v>
       </c>
       <c r="Q42" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>181</v>
       </c>
       <c r="R42" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>449</v>
       </c>
       <c r="S42" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>420</v>
       </c>
       <c r="T42" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.839779005524862</v>
       </c>
       <c r="U42" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.519337016574585</v>
       </c>
       <c r="V42" s="16">
@@ -6058,18 +6162,18 @@
       </c>
       <c r="AF42" s="16"/>
       <c r="AG42" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>449</v>
       </c>
       <c r="AH42" s="6">
         <v>5</v>
       </c>
       <c r="AI42" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>84</v>
       </c>
       <c r="AJ42" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>420</v>
       </c>
       <c r="AK42" s="16">
@@ -6079,10 +6183,13 @@
         <v>144</v>
       </c>
       <c r="AM42" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.58333333333333337</v>
       </c>
-      <c r="AN42" s="16"/>
+      <c r="AN42" s="16">
+        <f t="shared" si="6"/>
+        <v>181</v>
+      </c>
       <c r="AO42" s="16"/>
       <c r="AP42" s="16"/>
       <c r="AQ42" s="16"/>
@@ -6124,7 +6231,7 @@
         <v>74</v>
       </c>
       <c r="L43" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M43" s="16"/>
@@ -6136,22 +6243,22 @@
         <v>192</v>
       </c>
       <c r="Q43" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>14.8</v>
       </c>
       <c r="R43" s="4"/>
       <c r="S43" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T43" s="16">
-        <f t="shared" si="15"/>
-        <v>25.878378378378375</v>
-      </c>
-      <c r="U43" s="16">
         <f t="shared" si="16"/>
         <v>25.878378378378375</v>
       </c>
+      <c r="U43" s="16">
+        <f t="shared" si="17"/>
+        <v>25.878378378378375</v>
+      </c>
       <c r="V43" s="16">
         <v>25.8</v>
       </c>
@@ -6184,18 +6291,18 @@
       </c>
       <c r="AF43" s="16"/>
       <c r="AG43" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH43" s="6">
         <v>16</v>
       </c>
       <c r="AI43" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ43" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK43" s="16">
@@ -6205,10 +6312,13 @@
         <v>84</v>
       </c>
       <c r="AM43" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN43" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN43" s="16">
+        <f t="shared" si="6"/>
+        <v>5.9200000000000008</v>
+      </c>
       <c r="AO43" s="16"/>
       <c r="AP43" s="16"/>
       <c r="AQ43" s="16"/>
@@ -6252,7 +6362,7 @@
         <v>313</v>
       </c>
       <c r="L44" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-23</v>
       </c>
       <c r="M44" s="16"/>
@@ -6264,23 +6374,23 @@
         <v>240</v>
       </c>
       <c r="Q44" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>58</v>
       </c>
       <c r="R44" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>240</v>
       </c>
       <c r="S44" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>240</v>
       </c>
       <c r="T44" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14</v>
       </c>
       <c r="U44" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>9.862068965517242</v>
       </c>
       <c r="V44" s="16">
@@ -6315,18 +6425,18 @@
       </c>
       <c r="AF44" s="16"/>
       <c r="AG44" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>168</v>
       </c>
       <c r="AH44" s="6">
         <v>10</v>
       </c>
       <c r="AI44" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>24</v>
       </c>
       <c r="AJ44" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>168</v>
       </c>
       <c r="AK44" s="16">
@@ -6336,10 +6446,13 @@
         <v>84</v>
       </c>
       <c r="AM44" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN44" s="16"/>
+      <c r="AN44" s="16">
+        <f t="shared" si="6"/>
+        <v>40.599999999999994</v>
+      </c>
       <c r="AO44" s="16"/>
       <c r="AP44" s="16"/>
       <c r="AQ44" s="16"/>
@@ -6383,7 +6496,7 @@
         <v>123</v>
       </c>
       <c r="L45" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-3</v>
       </c>
       <c r="M45" s="16"/>
@@ -6395,22 +6508,22 @@
         <v>0</v>
       </c>
       <c r="Q45" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>24</v>
       </c>
       <c r="R45" s="4"/>
       <c r="S45" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T45" s="16">
-        <f t="shared" si="15"/>
-        <v>21.541666666666668</v>
-      </c>
-      <c r="U45" s="16">
         <f t="shared" si="16"/>
         <v>21.541666666666668</v>
       </c>
+      <c r="U45" s="16">
+        <f t="shared" si="17"/>
+        <v>21.541666666666668</v>
+      </c>
       <c r="V45" s="16">
         <v>36.4</v>
       </c>
@@ -6443,18 +6556,18 @@
       </c>
       <c r="AF45" s="16"/>
       <c r="AG45" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH45" s="6">
         <v>16</v>
       </c>
       <c r="AI45" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ45" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK45" s="16">
@@ -6464,10 +6577,13 @@
         <v>84</v>
       </c>
       <c r="AM45" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN45" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN45" s="16">
+        <f t="shared" si="6"/>
+        <v>9.6000000000000014</v>
+      </c>
       <c r="AO45" s="16"/>
       <c r="AP45" s="16"/>
       <c r="AQ45" s="16"/>
@@ -6511,7 +6627,7 @@
         <v>407</v>
       </c>
       <c r="L46" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-13</v>
       </c>
       <c r="M46" s="16"/>
@@ -6523,22 +6639,22 @@
         <v>240</v>
       </c>
       <c r="Q46" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>78.8</v>
       </c>
       <c r="R46" s="4"/>
       <c r="S46" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T46" s="16">
-        <f t="shared" si="15"/>
-        <v>14.923857868020304</v>
-      </c>
-      <c r="U46" s="16">
         <f t="shared" si="16"/>
         <v>14.923857868020304</v>
       </c>
+      <c r="U46" s="16">
+        <f t="shared" si="17"/>
+        <v>14.923857868020304</v>
+      </c>
       <c r="V46" s="16">
         <v>85.6</v>
       </c>
@@ -6571,18 +6687,18 @@
       </c>
       <c r="AF46" s="16"/>
       <c r="AG46" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH46" s="6">
         <v>10</v>
       </c>
       <c r="AI46" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ46" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK46" s="16">
@@ -6592,10 +6708,13 @@
         <v>84</v>
       </c>
       <c r="AM46" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN46" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN46" s="16">
+        <f t="shared" si="6"/>
+        <v>55.16</v>
+      </c>
       <c r="AO46" s="16"/>
       <c r="AP46" s="16"/>
       <c r="AQ46" s="16"/>
@@ -6639,7 +6758,7 @@
         <v>171</v>
       </c>
       <c r="L47" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M47" s="16"/>
@@ -6651,22 +6770,22 @@
         <v>120</v>
       </c>
       <c r="Q47" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34.200000000000003</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T47" s="16">
-        <f t="shared" si="15"/>
-        <v>13.245614035087717</v>
-      </c>
-      <c r="U47" s="16">
         <f t="shared" si="16"/>
         <v>13.245614035087717</v>
       </c>
+      <c r="U47" s="16">
+        <f t="shared" si="17"/>
+        <v>13.245614035087717</v>
+      </c>
       <c r="V47" s="16">
         <v>30.6</v>
       </c>
@@ -6699,18 +6818,18 @@
       </c>
       <c r="AF47" s="16"/>
       <c r="AG47" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH47" s="6">
         <v>10</v>
       </c>
       <c r="AI47" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ47" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK47" s="16">
@@ -6720,10 +6839,13 @@
         <v>84</v>
       </c>
       <c r="AM47" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN47" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN47" s="16">
+        <f t="shared" si="6"/>
+        <v>23.94</v>
+      </c>
       <c r="AO47" s="16"/>
       <c r="AP47" s="16"/>
       <c r="AQ47" s="16"/>
@@ -6767,7 +6889,7 @@
         <v>373</v>
       </c>
       <c r="L48" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-4</v>
       </c>
       <c r="M48" s="16"/>
@@ -6779,22 +6901,22 @@
         <v>480</v>
       </c>
       <c r="Q48" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>73.8</v>
       </c>
       <c r="R48" s="4"/>
       <c r="S48" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="T48" s="16">
-        <f t="shared" si="15"/>
-        <v>17.168021680216803</v>
-      </c>
-      <c r="U48" s="16">
         <f t="shared" si="16"/>
         <v>17.168021680216803</v>
       </c>
+      <c r="U48" s="16">
+        <f t="shared" si="17"/>
+        <v>17.168021680216803</v>
+      </c>
       <c r="V48" s="16">
         <v>48.6</v>
       </c>
@@ -6827,18 +6949,18 @@
       </c>
       <c r="AF48" s="16"/>
       <c r="AG48" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="AH48" s="6">
         <v>8</v>
       </c>
       <c r="AI48" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AJ48" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AK48" s="16">
@@ -6848,10 +6970,13 @@
         <v>84</v>
       </c>
       <c r="AM48" s="8">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="AN48" s="16"/>
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="AN48" s="16">
+        <f t="shared" si="6"/>
+        <v>59.04</v>
+      </c>
       <c r="AO48" s="16"/>
       <c r="AP48" s="16"/>
       <c r="AQ48" s="16"/>
@@ -6895,7 +7020,7 @@
         <v>739</v>
       </c>
       <c r="L49" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-13</v>
       </c>
       <c r="M49" s="16"/>
@@ -6907,23 +7032,23 @@
         <v>780</v>
       </c>
       <c r="Q49" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>145.19999999999999</v>
       </c>
       <c r="R49" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>303.79999999999973</v>
       </c>
       <c r="S49" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>300</v>
       </c>
       <c r="T49" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>13.97382920110193</v>
       </c>
       <c r="U49" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>11.90771349862259</v>
       </c>
       <c r="V49" s="16">
@@ -6958,18 +7083,18 @@
       </c>
       <c r="AF49" s="16"/>
       <c r="AG49" s="16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>303.79999999999973</v>
       </c>
       <c r="AH49" s="6">
         <v>5</v>
       </c>
       <c r="AI49" s="8">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>60</v>
       </c>
       <c r="AJ49" s="16">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>300</v>
       </c>
       <c r="AK49" s="16">
@@ -6979,10 +7104,13 @@
         <v>84</v>
       </c>
       <c r="AM49" s="8">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="AN49" s="16"/>
+      <c r="AN49" s="16">
+        <f t="shared" si="6"/>
+        <v>145.19999999999999</v>
+      </c>
       <c r="AO49" s="16"/>
       <c r="AP49" s="16"/>
       <c r="AQ49" s="16"/>
@@ -7026,7 +7154,7 @@
         <v>213</v>
       </c>
       <c r="L50" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-3</v>
       </c>
       <c r="M50" s="16"/>
@@ -7038,23 +7166,23 @@
         <v>0</v>
       </c>
       <c r="Q50" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>42</v>
       </c>
       <c r="R50" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>154</v>
       </c>
       <c r="S50" s="4">
-        <f t="shared" ref="S50:S71" si="17">AH50*AI50</f>
+        <f t="shared" ref="S50:S71" si="18">AH50*AI50</f>
         <v>192</v>
       </c>
       <c r="T50" s="16">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>14.904761904761905</v>
       </c>
       <c r="U50" s="16">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>10.333333333333334</v>
       </c>
       <c r="V50" s="16">
@@ -7089,18 +7217,18 @@
       </c>
       <c r="AF50" s="16"/>
       <c r="AG50" s="16">
-        <f t="shared" ref="AG50:AG71" si="18">G50*R50</f>
+        <f t="shared" ref="AG50:AG71" si="19">G50*R50</f>
         <v>138.6</v>
       </c>
       <c r="AH50" s="6">
         <v>8</v>
       </c>
       <c r="AI50" s="8">
-        <f t="shared" ref="AI50:AI71" si="19">MROUND(R50, AH50*AK50)/AH50</f>
+        <f t="shared" ref="AI50:AI71" si="20">MROUND(R50, AH50*AK50)/AH50</f>
         <v>24</v>
       </c>
       <c r="AJ50" s="16">
-        <f t="shared" ref="AJ50:AJ71" si="20">AI50*AH50*G50</f>
+        <f t="shared" ref="AJ50:AJ71" si="21">AI50*AH50*G50</f>
         <v>172.8</v>
       </c>
       <c r="AK50" s="16">
@@ -7110,10 +7238,13 @@
         <v>84</v>
       </c>
       <c r="AM50" s="8">
-        <f t="shared" ref="AM50:AM71" si="21">AI50/AL50</f>
+        <f t="shared" ref="AM50:AM71" si="22">AI50/AL50</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="AN50" s="16"/>
+      <c r="AN50" s="16">
+        <f t="shared" si="6"/>
+        <v>37.800000000000004</v>
+      </c>
       <c r="AO50" s="16"/>
       <c r="AP50" s="16"/>
       <c r="AQ50" s="16"/>
@@ -7157,7 +7288,7 @@
         <v>90</v>
       </c>
       <c r="L51" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-3</v>
       </c>
       <c r="M51" s="16"/>
@@ -7169,22 +7300,22 @@
         <v>96</v>
       </c>
       <c r="Q51" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>17.399999999999999</v>
       </c>
       <c r="R51" s="4"/>
       <c r="S51" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T51" s="16">
-        <f t="shared" si="15"/>
-        <v>12.931034482758621</v>
-      </c>
-      <c r="U51" s="16">
         <f t="shared" si="16"/>
         <v>12.931034482758621</v>
       </c>
+      <c r="U51" s="16">
+        <f t="shared" si="17"/>
+        <v>12.931034482758621</v>
+      </c>
       <c r="V51" s="16">
         <v>16.8</v>
       </c>
@@ -7217,18 +7348,18 @@
       </c>
       <c r="AF51" s="16"/>
       <c r="AG51" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH51" s="6">
         <v>8</v>
       </c>
       <c r="AI51" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ51" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK51" s="16">
@@ -7238,10 +7369,13 @@
         <v>84</v>
       </c>
       <c r="AM51" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN51" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN51" s="16">
+        <f t="shared" si="6"/>
+        <v>15.659999999999998</v>
+      </c>
       <c r="AO51" s="16"/>
       <c r="AP51" s="16"/>
       <c r="AQ51" s="16"/>
@@ -7285,7 +7419,7 @@
         <v>345</v>
       </c>
       <c r="L52" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M52" s="16"/>
@@ -7297,23 +7431,23 @@
         <v>240</v>
       </c>
       <c r="Q52" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>69</v>
       </c>
       <c r="R52" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>226</v>
       </c>
       <c r="S52" s="4">
+        <f t="shared" si="18"/>
+        <v>240</v>
+      </c>
+      <c r="T52" s="16">
+        <f t="shared" si="16"/>
+        <v>14.202898550724637</v>
+      </c>
+      <c r="U52" s="16">
         <f t="shared" si="17"/>
-        <v>240</v>
-      </c>
-      <c r="T52" s="16">
-        <f t="shared" si="15"/>
-        <v>14.202898550724637</v>
-      </c>
-      <c r="U52" s="16">
-        <f t="shared" si="16"/>
         <v>10.72463768115942</v>
       </c>
       <c r="V52" s="16">
@@ -7348,18 +7482,18 @@
       </c>
       <c r="AF52" s="16"/>
       <c r="AG52" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>226</v>
       </c>
       <c r="AH52" s="6">
         <v>5</v>
       </c>
       <c r="AI52" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>48</v>
       </c>
       <c r="AJ52" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>240</v>
       </c>
       <c r="AK52" s="16">
@@ -7369,10 +7503,13 @@
         <v>144</v>
       </c>
       <c r="AM52" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.33333333333333331</v>
       </c>
-      <c r="AN52" s="16"/>
+      <c r="AN52" s="16">
+        <f t="shared" si="6"/>
+        <v>69</v>
+      </c>
       <c r="AO52" s="16"/>
       <c r="AP52" s="16"/>
       <c r="AQ52" s="16"/>
@@ -7406,7 +7543,7 @@
       <c r="J53" s="16"/>
       <c r="K53" s="16"/>
       <c r="L53" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M53" s="16"/>
@@ -7418,22 +7555,22 @@
         <v>600</v>
       </c>
       <c r="Q53" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R53" s="4"/>
       <c r="S53" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T53" s="16" t="e">
-        <f t="shared" si="15"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U53" s="16" t="e">
         <f t="shared" si="16"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="U53" s="16" t="e">
+        <f t="shared" si="17"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="V53" s="16">
         <v>0</v>
       </c>
@@ -7468,18 +7605,18 @@
         <v>140</v>
       </c>
       <c r="AG53" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH53" s="6">
         <v>5</v>
       </c>
       <c r="AI53" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ53" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK53" s="16">
@@ -7489,10 +7626,13 @@
         <v>84</v>
       </c>
       <c r="AM53" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN53" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN53" s="16">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AO53" s="16"/>
       <c r="AP53" s="16"/>
       <c r="AQ53" s="16"/>
@@ -7536,7 +7676,7 @@
         <v>414.4</v>
       </c>
       <c r="L54" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-11.099999999999966</v>
       </c>
       <c r="M54" s="16"/>
@@ -7548,22 +7688,22 @@
         <v>310.8</v>
       </c>
       <c r="Q54" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>80.66</v>
       </c>
       <c r="R54" s="4"/>
       <c r="S54" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T54" s="16">
-        <f t="shared" si="15"/>
-        <v>14.174311926605505</v>
-      </c>
-      <c r="U54" s="16">
         <f t="shared" si="16"/>
         <v>14.174311926605505</v>
       </c>
+      <c r="U54" s="16">
+        <f t="shared" si="17"/>
+        <v>14.174311926605505</v>
+      </c>
       <c r="V54" s="16">
         <v>81.400000000000006</v>
       </c>
@@ -7596,18 +7736,18 @@
       </c>
       <c r="AF54" s="16"/>
       <c r="AG54" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH54" s="6">
         <v>3.7</v>
       </c>
       <c r="AI54" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ54" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK54" s="16">
@@ -7617,10 +7757,13 @@
         <v>126</v>
       </c>
       <c r="AM54" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN54" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN54" s="16">
+        <f t="shared" si="6"/>
+        <v>80.66</v>
+      </c>
       <c r="AO54" s="16"/>
       <c r="AP54" s="16"/>
       <c r="AQ54" s="16"/>
@@ -7664,7 +7807,7 @@
         <v>260</v>
       </c>
       <c r="L55" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M55" s="16"/>
@@ -7676,22 +7819,22 @@
         <v>0</v>
       </c>
       <c r="Q55" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>52</v>
       </c>
       <c r="R55" s="4"/>
       <c r="S55" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T55" s="16">
-        <f t="shared" si="15"/>
-        <v>18.807692307692307</v>
-      </c>
-      <c r="U55" s="16">
         <f t="shared" si="16"/>
         <v>18.807692307692307</v>
       </c>
+      <c r="U55" s="16">
+        <f t="shared" si="17"/>
+        <v>18.807692307692307</v>
+      </c>
       <c r="V55" s="16">
         <v>43.6</v>
       </c>
@@ -7726,18 +7869,18 @@
         <v>145</v>
       </c>
       <c r="AG55" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH55" s="6">
         <v>30</v>
       </c>
       <c r="AI55" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ55" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK55" s="16">
@@ -7747,10 +7890,13 @@
         <v>126</v>
       </c>
       <c r="AM55" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN55" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN55" s="16">
+        <f t="shared" si="6"/>
+        <v>4.68</v>
+      </c>
       <c r="AO55" s="16"/>
       <c r="AP55" s="16"/>
       <c r="AQ55" s="16"/>
@@ -7794,7 +7940,7 @@
         <v>191</v>
       </c>
       <c r="L56" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-16</v>
       </c>
       <c r="M56" s="16"/>
@@ -7806,22 +7952,22 @@
         <v>420</v>
       </c>
       <c r="Q56" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>35</v>
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T56" s="16">
-        <f t="shared" si="15"/>
-        <v>14.228571428571428</v>
-      </c>
-      <c r="U56" s="16">
         <f t="shared" si="16"/>
         <v>14.228571428571428</v>
       </c>
+      <c r="U56" s="16">
+        <f t="shared" si="17"/>
+        <v>14.228571428571428</v>
+      </c>
       <c r="V56" s="16">
         <v>36</v>
       </c>
@@ -7854,18 +8000,18 @@
       </c>
       <c r="AF56" s="16"/>
       <c r="AG56" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH56" s="6">
         <v>6</v>
       </c>
       <c r="AI56" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ56" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK56" s="16">
@@ -7875,10 +8021,13 @@
         <v>140</v>
       </c>
       <c r="AM56" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN56" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN56" s="16">
+        <f t="shared" si="6"/>
+        <v>8.0500000000000007</v>
+      </c>
       <c r="AO56" s="16"/>
       <c r="AP56" s="16"/>
       <c r="AQ56" s="16"/>
@@ -7924,7 +8073,7 @@
         <v>625</v>
       </c>
       <c r="L57" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-78</v>
       </c>
       <c r="M57" s="16"/>
@@ -7936,22 +8085,22 @@
         <v>0</v>
       </c>
       <c r="Q57" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>109.4</v>
       </c>
       <c r="R57" s="4"/>
       <c r="S57" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T57" s="16">
-        <f t="shared" si="15"/>
-        <v>16.9926873857404</v>
-      </c>
-      <c r="U57" s="16">
         <f t="shared" si="16"/>
         <v>16.9926873857404</v>
       </c>
+      <c r="U57" s="16">
+        <f t="shared" si="17"/>
+        <v>16.9926873857404</v>
+      </c>
       <c r="V57" s="16">
         <v>89.6</v>
       </c>
@@ -7984,18 +8133,18 @@
       </c>
       <c r="AF57" s="16"/>
       <c r="AG57" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH57" s="6">
         <v>12</v>
       </c>
       <c r="AI57" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ57" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK57" s="16">
@@ -8005,10 +8154,13 @@
         <v>70</v>
       </c>
       <c r="AM57" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN57" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN57" s="16">
+        <f t="shared" si="6"/>
+        <v>27.35</v>
+      </c>
       <c r="AO57" s="16"/>
       <c r="AP57" s="16"/>
       <c r="AQ57" s="16"/>
@@ -8052,7 +8204,7 @@
         <v>410</v>
       </c>
       <c r="L58" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-33</v>
       </c>
       <c r="M58" s="16"/>
@@ -8064,22 +8216,22 @@
         <v>336</v>
       </c>
       <c r="Q58" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>75.400000000000006</v>
       </c>
       <c r="R58" s="4"/>
       <c r="S58" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T58" s="16">
-        <f t="shared" si="15"/>
-        <v>16.976127320954905</v>
-      </c>
-      <c r="U58" s="16">
         <f t="shared" si="16"/>
         <v>16.976127320954905</v>
       </c>
+      <c r="U58" s="16">
+        <f t="shared" si="17"/>
+        <v>16.976127320954905</v>
+      </c>
       <c r="V58" s="16">
         <v>95</v>
       </c>
@@ -8112,18 +8264,18 @@
       </c>
       <c r="AF58" s="16"/>
       <c r="AG58" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH58" s="6">
         <v>12</v>
       </c>
       <c r="AI58" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ58" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK58" s="16">
@@ -8133,10 +8285,13 @@
         <v>70</v>
       </c>
       <c r="AM58" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN58" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN58" s="16">
+        <f t="shared" si="6"/>
+        <v>18.850000000000001</v>
+      </c>
       <c r="AO58" s="16"/>
       <c r="AP58" s="16"/>
       <c r="AQ58" s="16"/>
@@ -8178,7 +8333,7 @@
         <v>1</v>
       </c>
       <c r="L59" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M59" s="16"/>
@@ -8190,22 +8345,22 @@
         <v>0</v>
       </c>
       <c r="Q59" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>0.2</v>
       </c>
       <c r="R59" s="4"/>
       <c r="S59" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T59" s="16">
-        <f t="shared" si="15"/>
-        <v>410</v>
-      </c>
-      <c r="U59" s="16">
         <f t="shared" si="16"/>
         <v>410</v>
       </c>
+      <c r="U59" s="16">
+        <f t="shared" si="17"/>
+        <v>410</v>
+      </c>
       <c r="V59" s="16">
         <v>0.6</v>
       </c>
@@ -8238,18 +8393,18 @@
       </c>
       <c r="AF59" s="16"/>
       <c r="AG59" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH59" s="6">
         <v>6</v>
       </c>
       <c r="AI59" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ59" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK59" s="16">
@@ -8259,10 +8414,13 @@
         <v>140</v>
       </c>
       <c r="AM59" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN59" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN59" s="16">
+        <f t="shared" si="6"/>
+        <v>3.5999999999999997E-2</v>
+      </c>
       <c r="AO59" s="16"/>
       <c r="AP59" s="16"/>
       <c r="AQ59" s="16"/>
@@ -8304,7 +8462,7 @@
         <v>17</v>
       </c>
       <c r="L60" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M60" s="16"/>
@@ -8316,22 +8474,22 @@
         <v>0</v>
       </c>
       <c r="Q60" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>3.4</v>
       </c>
       <c r="R60" s="4"/>
       <c r="S60" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T60" s="16">
-        <f t="shared" si="15"/>
-        <v>39.117647058823529</v>
-      </c>
-      <c r="U60" s="16">
         <f t="shared" si="16"/>
         <v>39.117647058823529</v>
       </c>
+      <c r="U60" s="16">
+        <f t="shared" si="17"/>
+        <v>39.117647058823529</v>
+      </c>
       <c r="V60" s="16">
         <v>3.2</v>
       </c>
@@ -8366,18 +8524,18 @@
         <v>155</v>
       </c>
       <c r="AG60" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH60" s="6">
         <v>6</v>
       </c>
       <c r="AI60" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ60" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK60" s="16">
@@ -8387,10 +8545,13 @@
         <v>140</v>
       </c>
       <c r="AM60" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN60" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN60" s="16">
+        <f t="shared" si="6"/>
+        <v>0.61199999999999999</v>
+      </c>
       <c r="AO60" s="16"/>
       <c r="AP60" s="16"/>
       <c r="AQ60" s="16"/>
@@ -8432,7 +8593,7 @@
         <v>12</v>
       </c>
       <c r="L61" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="M61" s="16"/>
@@ -8444,22 +8605,22 @@
         <v>0</v>
       </c>
       <c r="Q61" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>2.4</v>
       </c>
       <c r="R61" s="4"/>
       <c r="S61" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T61" s="16">
-        <f t="shared" si="15"/>
-        <v>64.166666666666671</v>
-      </c>
-      <c r="U61" s="16">
         <f t="shared" si="16"/>
         <v>64.166666666666671</v>
       </c>
+      <c r="U61" s="16">
+        <f t="shared" si="17"/>
+        <v>64.166666666666671</v>
+      </c>
       <c r="V61" s="16">
         <v>1</v>
       </c>
@@ -8494,18 +8655,18 @@
         <v>155</v>
       </c>
       <c r="AG61" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH61" s="6">
         <v>6</v>
       </c>
       <c r="AI61" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ61" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK61" s="16">
@@ -8515,10 +8676,13 @@
         <v>140</v>
       </c>
       <c r="AM61" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN61" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN61" s="16">
+        <f t="shared" si="6"/>
+        <v>0.432</v>
+      </c>
       <c r="AO61" s="16"/>
       <c r="AP61" s="16"/>
       <c r="AQ61" s="16"/>
@@ -8562,7 +8726,7 @@
         <v>569</v>
       </c>
       <c r="L62" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-1</v>
       </c>
       <c r="M62" s="16"/>
@@ -8574,22 +8738,22 @@
         <v>168</v>
       </c>
       <c r="Q62" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>113.6</v>
       </c>
       <c r="R62" s="4"/>
       <c r="S62" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T62" s="16">
-        <f t="shared" si="15"/>
-        <v>15.246478873239438</v>
-      </c>
-      <c r="U62" s="16">
         <f t="shared" si="16"/>
         <v>15.246478873239438</v>
       </c>
+      <c r="U62" s="16">
+        <f t="shared" si="17"/>
+        <v>15.246478873239438</v>
+      </c>
       <c r="V62" s="16">
         <v>124.4</v>
       </c>
@@ -8622,18 +8786,18 @@
       </c>
       <c r="AF62" s="16"/>
       <c r="AG62" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH62" s="6">
         <v>12</v>
       </c>
       <c r="AI62" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ62" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK62" s="16">
@@ -8643,10 +8807,13 @@
         <v>70</v>
       </c>
       <c r="AM62" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN62" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN62" s="16">
+        <f t="shared" si="6"/>
+        <v>34.08</v>
+      </c>
       <c r="AO62" s="16"/>
       <c r="AP62" s="16"/>
       <c r="AQ62" s="16"/>
@@ -8690,7 +8857,7 @@
         <v>462</v>
       </c>
       <c r="L63" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-5</v>
       </c>
       <c r="M63" s="16"/>
@@ -8702,22 +8869,22 @@
         <v>672</v>
       </c>
       <c r="Q63" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>91.4</v>
       </c>
       <c r="R63" s="4"/>
       <c r="S63" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T63" s="16">
-        <f t="shared" si="15"/>
-        <v>18.249452954048138</v>
-      </c>
-      <c r="U63" s="16">
         <f t="shared" si="16"/>
         <v>18.249452954048138</v>
       </c>
+      <c r="U63" s="16">
+        <f t="shared" si="17"/>
+        <v>18.249452954048138</v>
+      </c>
       <c r="V63" s="16">
         <v>116</v>
       </c>
@@ -8750,18 +8917,18 @@
       </c>
       <c r="AF63" s="16"/>
       <c r="AG63" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH63" s="6">
         <v>12</v>
       </c>
       <c r="AI63" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ63" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK63" s="16">
@@ -8771,10 +8938,13 @@
         <v>70</v>
       </c>
       <c r="AM63" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN63" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN63" s="16">
+        <f t="shared" si="6"/>
+        <v>27.42</v>
+      </c>
       <c r="AO63" s="16"/>
       <c r="AP63" s="16"/>
       <c r="AQ63" s="16"/>
@@ -8818,7 +8988,7 @@
         <v>208</v>
       </c>
       <c r="L64" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-14</v>
       </c>
       <c r="M64" s="16"/>
@@ -8830,22 +9000,22 @@
         <v>196</v>
       </c>
       <c r="Q64" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>38.799999999999997</v>
       </c>
       <c r="R64" s="4"/>
       <c r="S64" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T64" s="16">
-        <f t="shared" si="15"/>
-        <v>17.061855670103093</v>
-      </c>
-      <c r="U64" s="16">
         <f t="shared" si="16"/>
         <v>17.061855670103093</v>
       </c>
+      <c r="U64" s="16">
+        <f t="shared" si="17"/>
+        <v>17.061855670103093</v>
+      </c>
       <c r="V64" s="16">
         <v>37.6</v>
       </c>
@@ -8878,18 +9048,18 @@
       </c>
       <c r="AF64" s="16"/>
       <c r="AG64" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH64" s="6">
         <v>14</v>
       </c>
       <c r="AI64" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ64" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK64" s="16">
@@ -8899,10 +9069,13 @@
         <v>70</v>
       </c>
       <c r="AM64" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN64" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN64" s="16">
+        <f t="shared" si="6"/>
+        <v>11.639999999999999</v>
+      </c>
       <c r="AO64" s="16"/>
       <c r="AP64" s="16"/>
       <c r="AQ64" s="16"/>
@@ -8942,7 +9115,7 @@
         <v>263</v>
       </c>
       <c r="L65" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-92</v>
       </c>
       <c r="M65" s="16"/>
@@ -8954,22 +9127,22 @@
         <v>672</v>
       </c>
       <c r="Q65" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>34.200000000000003</v>
       </c>
       <c r="R65" s="4"/>
       <c r="S65" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T65" s="16">
-        <f t="shared" si="15"/>
-        <v>19.736842105263158</v>
-      </c>
-      <c r="U65" s="16">
         <f t="shared" si="16"/>
         <v>19.736842105263158</v>
       </c>
+      <c r="U65" s="16">
+        <f t="shared" si="17"/>
+        <v>19.736842105263158</v>
+      </c>
       <c r="V65" s="16">
         <v>50.6</v>
       </c>
@@ -9004,18 +9177,18 @@
         <v>166</v>
       </c>
       <c r="AG65" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH65" s="6">
         <v>6</v>
       </c>
       <c r="AI65" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ65" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK65" s="16">
@@ -9025,10 +9198,13 @@
         <v>140</v>
       </c>
       <c r="AM65" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN65" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN65" s="16">
+        <f t="shared" si="6"/>
+        <v>7.5240000000000009</v>
+      </c>
       <c r="AO65" s="16"/>
       <c r="AP65" s="16"/>
       <c r="AQ65" s="16"/>
@@ -9072,7 +9248,7 @@
         <v>1456</v>
       </c>
       <c r="L66" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-78</v>
       </c>
       <c r="M66" s="16"/>
@@ -9084,22 +9260,22 @@
         <v>0</v>
       </c>
       <c r="Q66" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>275.60000000000002</v>
       </c>
       <c r="R66" s="4"/>
       <c r="S66" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T66" s="16">
-        <f t="shared" si="15"/>
-        <v>16.788824383164005</v>
-      </c>
-      <c r="U66" s="16">
         <f t="shared" si="16"/>
         <v>16.788824383164005</v>
       </c>
+      <c r="U66" s="16">
+        <f t="shared" si="17"/>
+        <v>16.788824383164005</v>
+      </c>
       <c r="V66" s="16">
         <v>283.2</v>
       </c>
@@ -9132,18 +9308,18 @@
       </c>
       <c r="AF66" s="16"/>
       <c r="AG66" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH66" s="6">
         <v>12</v>
       </c>
       <c r="AI66" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ66" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK66" s="16">
@@ -9153,10 +9329,13 @@
         <v>70</v>
       </c>
       <c r="AM66" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN66" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN66" s="16">
+        <f t="shared" si="6"/>
+        <v>68.900000000000006</v>
+      </c>
       <c r="AO66" s="16"/>
       <c r="AP66" s="16"/>
       <c r="AQ66" s="16"/>
@@ -9200,7 +9379,7 @@
         <v>1461</v>
       </c>
       <c r="L67" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-118</v>
       </c>
       <c r="M67" s="16"/>
@@ -9212,22 +9391,22 @@
         <v>0</v>
       </c>
       <c r="Q67" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>268.60000000000002</v>
       </c>
       <c r="R67" s="4"/>
       <c r="S67" s="4">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T67" s="16">
-        <f t="shared" si="15"/>
-        <v>13.946388682055099</v>
-      </c>
-      <c r="U67" s="16">
         <f t="shared" si="16"/>
         <v>13.946388682055099</v>
       </c>
+      <c r="U67" s="16">
+        <f t="shared" si="17"/>
+        <v>13.946388682055099</v>
+      </c>
       <c r="V67" s="16">
         <v>244.6</v>
       </c>
@@ -9260,18 +9439,18 @@
       </c>
       <c r="AF67" s="16"/>
       <c r="AG67" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AH67" s="6">
         <v>12</v>
       </c>
       <c r="AI67" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AJ67" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="AK67" s="16">
@@ -9281,10 +9460,13 @@
         <v>70</v>
       </c>
       <c r="AM67" s="8">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AN67" s="16"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
+      </c>
+      <c r="AN67" s="16">
+        <f t="shared" si="6"/>
+        <v>67.150000000000006</v>
+      </c>
       <c r="AO67" s="16"/>
       <c r="AP67" s="16"/>
       <c r="AQ67" s="16"/>
@@ -9328,7 +9510,7 @@
         <v>518</v>
       </c>
       <c r="L68" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-12</v>
       </c>
       <c r="M68" s="16"/>
@@ -9340,23 +9522,23 @@
         <v>924</v>
       </c>
       <c r="Q68" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>101.2</v>
       </c>
       <c r="R68" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>159.79999999999995</v>
       </c>
       <c r="S68" s="4">
+        <f t="shared" si="18"/>
+        <v>168</v>
+      </c>
+      <c r="T68" s="16">
+        <f t="shared" si="16"/>
+        <v>14.081027667984189</v>
+      </c>
+      <c r="U68" s="16">
         <f t="shared" si="17"/>
-        <v>168</v>
-      </c>
-      <c r="T68" s="16">
-        <f t="shared" si="15"/>
-        <v>14.081027667984189</v>
-      </c>
-      <c r="U68" s="16">
-        <f t="shared" si="16"/>
         <v>12.420948616600791</v>
       </c>
       <c r="V68" s="16">
@@ -9391,18 +9573,18 @@
       </c>
       <c r="AF68" s="16"/>
       <c r="AG68" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>36.753999999999991</v>
       </c>
       <c r="AH68" s="6">
         <v>6</v>
       </c>
       <c r="AI68" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>28</v>
       </c>
       <c r="AJ68" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>38.64</v>
       </c>
       <c r="AK68" s="16">
@@ -9412,10 +9594,13 @@
         <v>140</v>
       </c>
       <c r="AM68" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.2</v>
       </c>
-      <c r="AN68" s="16"/>
+      <c r="AN68" s="16">
+        <f t="shared" si="6"/>
+        <v>23.276000000000003</v>
+      </c>
       <c r="AO68" s="16"/>
       <c r="AP68" s="16"/>
       <c r="AQ68" s="16"/>
@@ -9457,7 +9642,7 @@
         <v>709</v>
       </c>
       <c r="L69" s="16">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>-74</v>
       </c>
       <c r="M69" s="16"/>
@@ -9469,23 +9654,23 @@
         <v>1428</v>
       </c>
       <c r="Q69" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>127</v>
       </c>
       <c r="R69" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>303</v>
       </c>
       <c r="S69" s="4">
+        <f t="shared" si="18"/>
+        <v>336</v>
+      </c>
+      <c r="T69" s="16">
+        <f t="shared" si="16"/>
+        <v>14.259842519685039</v>
+      </c>
+      <c r="U69" s="16">
         <f t="shared" si="17"/>
-        <v>336</v>
-      </c>
-      <c r="T69" s="16">
-        <f t="shared" si="15"/>
-        <v>14.259842519685039</v>
-      </c>
-      <c r="U69" s="16">
-        <f t="shared" si="16"/>
         <v>11.614173228346457</v>
       </c>
       <c r="V69" s="16">
@@ -9522,18 +9707,18 @@
         <v>166</v>
       </c>
       <c r="AG69" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>69.69</v>
       </c>
       <c r="AH69" s="6">
         <v>6</v>
       </c>
       <c r="AI69" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>56</v>
       </c>
       <c r="AJ69" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>77.28</v>
       </c>
       <c r="AK69" s="16">
@@ -9543,10 +9728,13 @@
         <v>140</v>
       </c>
       <c r="AM69" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.4</v>
       </c>
-      <c r="AN69" s="16"/>
+      <c r="AN69" s="16">
+        <f t="shared" si="6"/>
+        <v>29.21</v>
+      </c>
       <c r="AO69" s="16"/>
       <c r="AP69" s="16"/>
       <c r="AQ69" s="16"/>
@@ -9590,7 +9778,7 @@
         <v>158.5</v>
       </c>
       <c r="L70" s="16">
-        <f t="shared" ref="L70:L71" si="22">E70-K70</f>
+        <f t="shared" ref="L70:L71" si="23">E70-K70</f>
         <v>-1.9000000000000057</v>
       </c>
       <c r="M70" s="16"/>
@@ -9602,23 +9790,23 @@
         <v>37.799999999999997</v>
       </c>
       <c r="Q70" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>31.32</v>
       </c>
       <c r="R70" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>49.480000000000018</v>
       </c>
       <c r="S70" s="4">
+        <f t="shared" si="18"/>
+        <v>37.800000000000004</v>
+      </c>
+      <c r="T70" s="16">
+        <f t="shared" ref="T70:T71" si="24">(F70+O70+P70+S70)/Q70</f>
+        <v>13.627075351213282</v>
+      </c>
+      <c r="U70" s="16">
         <f t="shared" si="17"/>
-        <v>37.800000000000004</v>
-      </c>
-      <c r="T70" s="16">
-        <f t="shared" ref="T70:T71" si="23">(F70+O70+P70+S70)/Q70</f>
-        <v>13.627075351213282</v>
-      </c>
-      <c r="U70" s="16">
-        <f t="shared" si="16"/>
         <v>12.420178799489145</v>
       </c>
       <c r="V70" s="16">
@@ -9653,18 +9841,18 @@
       </c>
       <c r="AF70" s="16"/>
       <c r="AG70" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>49.480000000000018</v>
       </c>
       <c r="AH70" s="6">
         <v>2.7</v>
       </c>
       <c r="AI70" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>14</v>
       </c>
       <c r="AJ70" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>37.800000000000004</v>
       </c>
       <c r="AK70" s="16">
@@ -9674,10 +9862,13 @@
         <v>126</v>
       </c>
       <c r="AM70" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0.1111111111111111</v>
       </c>
-      <c r="AN70" s="16"/>
+      <c r="AN70" s="16">
+        <f t="shared" si="6"/>
+        <v>31.32</v>
+      </c>
       <c r="AO70" s="16"/>
       <c r="AP70" s="16"/>
       <c r="AQ70" s="16"/>
@@ -9721,7 +9912,7 @@
         <v>1445.1</v>
       </c>
       <c r="L71" s="16">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>-10</v>
       </c>
       <c r="M71" s="16"/>
@@ -9733,23 +9924,23 @@
         <v>3180</v>
       </c>
       <c r="Q71" s="16">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>287.02</v>
       </c>
       <c r="R71" s="4">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>924.37999999999977</v>
       </c>
       <c r="S71" s="4">
+        <f t="shared" si="18"/>
+        <v>900</v>
+      </c>
+      <c r="T71" s="16">
+        <f t="shared" si="24"/>
+        <v>13.915058184098671</v>
+      </c>
+      <c r="U71" s="16">
         <f t="shared" si="17"/>
-        <v>900</v>
-      </c>
-      <c r="T71" s="16">
-        <f t="shared" si="23"/>
-        <v>13.915058184098671</v>
-      </c>
-      <c r="U71" s="16">
-        <f t="shared" si="16"/>
         <v>10.779388195944534</v>
       </c>
       <c r="V71" s="16">
@@ -9784,18 +9975,18 @@
       </c>
       <c r="AF71" s="16"/>
       <c r="AG71" s="16">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>924.37999999999977</v>
       </c>
       <c r="AH71" s="6">
         <v>5</v>
       </c>
       <c r="AI71" s="8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>180</v>
       </c>
       <c r="AJ71" s="16">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>900</v>
       </c>
       <c r="AK71" s="16">
@@ -9805,10 +9996,13 @@
         <v>84</v>
       </c>
       <c r="AM71" s="8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>2.1428571428571428</v>
       </c>
-      <c r="AN71" s="16"/>
+      <c r="AN71" s="16">
+        <f t="shared" ref="AN71" si="25">Q71*G71</f>
+        <v>287.02</v>
+      </c>
       <c r="AO71" s="16"/>
       <c r="AP71" s="16"/>
       <c r="AQ71" s="16"/>
